--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kalamata</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -685,22 +685,58 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -739,22 +739,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -797,22 +797,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -855,22 +855,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>21</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>

--- a/new-stats/panetolikos-fc.xlsx
+++ b/new-stats/panetolikos-fc.xlsx
@@ -913,22 +913,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AEK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Panetolikos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
